--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_315_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_315_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>65</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5079,13 +5079,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -6056,10 +6056,10 @@
         <v>15</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6448,16 +6448,16 @@
         <v>19</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
         <v>6</v>
@@ -6784,16 +6784,16 @@
         <v>80</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>20</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_315_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_315_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>87.50</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Y48" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="AA48" t="n">
